--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484140_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484140_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1483</v>
+        <v>2.3523</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8149</v>
+        <v>3.019</v>
       </c>
       <c r="F2" t="n">
         <v>-0.6667</v>
@@ -610,10 +610,10 @@
         <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7935</v>
+        <v>0.9976</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7483</v>
+        <v>0.9523</v>
       </c>
       <c r="U2" t="n">
         <v>0.0452</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3477</v>
+        <v>0.7312</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3455</v>
+        <v>1.7828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0022</v>
+        <v>-1.0516</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.497</v>
+        <v>1.3854</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9748</v>
+        <v>1.2443</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5222</v>
+        <v>0.1411</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6395999999999999</v>
+        <v>3.2743</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8405</v>
+        <v>1.4166</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2008</v>
+        <v>1.8576</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8573</v>
+        <v>-1.8888</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1343</v>
+        <v>-0.1723</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.723</v>
+        <v>-1.7165</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.1741</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2253</v>
+        <v>0.6037</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0836</v>
+        <v>0.4762</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1416</v>
+        <v>0.1274</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4129</v>
+        <v>-0.266</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0757</v>
+        <v>1.2065</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3373</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3857</v>
+        <v>0.3359</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7131999999999999</v>
+        <v>1.238</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0988</v>
+        <v>-0.9021</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.5847</v>
+        <v>-1.5469</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6475</v>
+        <v>-0.8667</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9371</v>
+        <v>-0.6802</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2829</v>
+        <v>1.7825</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1376</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1453</v>
+        <v>1.8525</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3018</v>
+        <v>-3.3294</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.51</v>
+        <v>-0.7967</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.7918</v>
+        <v>-2.5327</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9758</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9926</v>
+        <v>0.2877</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1622</v>
+        <v>0.1815</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1696</v>
+        <v>0.1062</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4129</v>
+        <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0162</v>
+        <v>0.266</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6032</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.471</v>
+        <v>-0.0581</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0856</v>
+        <v>-0.0602</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5566</v>
+        <v>0.0022</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3854</v>
+        <v>-3.497</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2443</v>
+        <v>-1.9748</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1411</v>
+        <v>-1.5222</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2743</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4166</v>
+        <v>-0.8405</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8576</v>
+        <v>0.2008</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8888</v>
+        <v>-2.8573</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1723</v>
+        <v>-1.1343</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7165</v>
+        <v>-1.723</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q5" t="n">
         <v>-3.1741</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5985</v>
+        <v>1.8195</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2209</v>
+        <v>1.6779</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3776</v>
+        <v>0.1416</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>2.4129</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>2.0757</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4724</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.2828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.9002</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2107</v>
+        <v>-1.183</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5469</v>
+        <v>-4.5847</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8667</v>
+        <v>-1.6475</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6802</v>
+        <v>-2.9371</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7825</v>
+        <v>-1.2829</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1376</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8525</v>
+        <v>-0.1453</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3294</v>
+        <v>-3.3018</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7967</v>
+        <v>-0.51</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5327</v>
+        <v>-2.7918</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>2.9758</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7181</v>
+        <v>1.0954</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5157</v>
+        <v>1.3492</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2024</v>
+        <v>-0.2538</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6032</v>
+        <v>2.4129</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>3.0162</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3373</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0483</v>
+        <v>-0.9182</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6622</v>
+        <v>-0.5602</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3861</v>
+        <v>-0.3581</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1213</v>
@@ -1000,13 +1000,13 @@
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3157</v>
+        <v>-0.1856</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2534</v>
+        <v>-0.2253</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3564</v>
+        <v>-1.2263</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3094</v>
+        <v>0.4114</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6658</v>
+        <v>-1.6378</v>
       </c>
       <c r="G8" t="n">
         <v>0.2835</v>
@@ -1078,13 +1078,13 @@
         <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1661</v>
+        <v>0.2962</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2438</v>
+        <v>0.3458</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0496</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0044</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8018</v>
+        <v>-2.196</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4239</v>
+        <v>0.2822</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2257</v>
+        <v>-2.4782</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4797</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5038</v>
+        <v>1.1096</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.7257</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6364</v>
+        <v>0.3839</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4129</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>F. LOPEZ BARCELO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7316</v>
+        <v>-3.5718</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7044</v>
+        <v>-2.4852</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0272</v>
+        <v>-1.0866</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2035</v>
+        <v>-3.7079</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1216</v>
+        <v>-0.4132</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0818</v>
+        <v>-3.2946</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7477</v>
+        <v>-1.9751</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3954</v>
+        <v>-0.0149</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6477000000000001</v>
+        <v>-1.9603</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4557</v>
+        <v>-1.7327</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7262</v>
+        <v>-0.3983</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7295</v>
+        <v>-1.3344</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7855</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9913</v>
+        <v>0.7312</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4534</v>
+        <v>0.4818</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4447</v>
+        <v>0.2494</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. LOPEZ BARCELO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.786</v>
+        <v>-4.2001</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5872</v>
+        <v>-2.4153</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1988</v>
+        <v>-1.7847</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7079</v>
+        <v>-3.2035</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4132</v>
+        <v>-2.1216</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2946</v>
+        <v>-1.0818</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9751</v>
+        <v>-0.7477</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0149</v>
+        <v>-1.3954</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9603</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7327</v>
+        <v>-2.4557</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3983</v>
+        <v>-0.7262</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3344</v>
+        <v>-1.7295</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5952</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>0.517</v>
+        <v>0.5229</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3798</v>
+        <v>-0.1643</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1372</v>
+        <v>0.6872</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6776</v>
+        <v>-4.4634</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2094</v>
+        <v>0.3114</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.887</v>
+        <v>-4.7748</v>
       </c>
       <c r="G12" t="n">
         <v>0.2556</v>
@@ -1390,13 +1390,13 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.322</v>
+        <v>-0.1077</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0113</v>
+        <v>0.1134</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3333</v>
+        <v>-0.2211</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6194</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.4323</v>
+        <v>-13.4973</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4889</v>
+        <v>2.4241</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.9212</v>
+        <v>-15.9214</v>
       </c>
       <c r="G13" t="n">
         <v>-15.5958</v>
@@ -1438,10 +1438,10 @@
         <v>-6.0727</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.5228</v>
+        <v>-9.522799999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8726</v>
+        <v>2.872599999999999</v>
       </c>
       <c r="K13" t="n">
         <v>-1.5314</v>
@@ -1453,7 +1453,7 @@
         <v>-18.4679</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.541499999999999</v>
+        <v>-4.5415</v>
       </c>
       <c r="O13" t="n">
         <v>-13.9265</v>
@@ -1468,13 +1468,13 @@
         <v>14.8789</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2353</v>
+        <v>7.1705</v>
       </c>
       <c r="T13" t="n">
-        <v>5.2441</v>
+        <v>6.179200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9911000000000001</v>
+        <v>0.9911000000000002</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0802</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.6958</v>
+        <v>10.2585</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2424</v>
+        <v>7.5485</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4533</v>
+        <v>2.71</v>
       </c>
       <c r="G14" t="n">
         <v>7.0929</v>
@@ -1546,13 +1546,13 @@
         <v>2.7774</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1891</v>
+        <v>-0.6264</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9748</v>
+        <v>-0.6687</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2143</v>
+        <v>0.0424</v>
       </c>
       <c r="V14" t="n">
         <v>1.0145</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.5077</v>
+        <v>9.4642</v>
       </c>
       <c r="E15" t="n">
         <v>5.5201</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9876</v>
+        <v>3.9441</v>
       </c>
       <c r="G15" t="n">
         <v>5.9437</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4279</v>
+        <v>0.5286</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0452</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3827</v>
+        <v>0.5738</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9122</v>
+        <v>7.714</v>
       </c>
       <c r="E16" t="n">
-        <v>4.508</v>
+        <v>4.61</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4043</v>
+        <v>3.104</v>
       </c>
       <c r="G16" t="n">
         <v>2.53</v>
@@ -1702,13 +1702,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8939</v>
+        <v>-0.0921</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1076</v>
+        <v>-0.0056</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7863</v>
+        <v>-0.0866</v>
       </c>
       <c r="V16" t="n">
         <v>2.8955</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8579</v>
+        <v>1.8213</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7805</v>
+        <v>2.3724</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9226</v>
+        <v>-0.551</v>
       </c>
       <c r="G17" t="n">
         <v>0.9923999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0354</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6236</v>
+        <v>0.2155</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5517</v>
+        <v>-0.1801</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3814</v>
+        <v>1.7113</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5201</v>
+        <v>2.418</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1387</v>
+        <v>-0.7067</v>
       </c>
       <c r="G18" t="n">
         <v>1.4862</v>
@@ -1858,13 +1858,13 @@
         <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2142</v>
+        <v>0.5441</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1191</v>
+        <v>0.0171</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0951</v>
+        <v>0.5271</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1206</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0641</v>
+        <v>1.3107</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1702</v>
+        <v>0.1359</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1061</v>
+        <v>1.1748</v>
       </c>
       <c r="G19" t="n">
         <v>0.887</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4074</v>
+        <v>-0.0326</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3174</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7839</v>
+        <v>0.2848</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3373</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3695</v>
+        <v>0.6108</v>
       </c>
       <c r="E20" t="n">
-        <v>1.325</v>
+        <v>1.7331</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6945</v>
+        <v>-1.1223</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1285</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4267</v>
+        <v>-0.4464</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8105</v>
+        <v>-0.4024</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6162</v>
+        <v>-0.044</v>
       </c>
       <c r="V20" t="n">
         <v>3.7647</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.252</v>
+        <v>-0.9119</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0293</v>
+        <v>-0.8253</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2226</v>
+        <v>-0.0866</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3766</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0737</v>
+        <v>0.2664</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U21" t="n">
-        <v>0.238</v>
+        <v>0.3741</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0455</v>
+        <v>-1.9698</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9741</v>
+        <v>-2.3822</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0713</v>
+        <v>0.4125</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1493</v>
@@ -2170,13 +2170,13 @@
         <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2941</v>
+        <v>0.3698</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2551</v>
+        <v>-0.153</v>
       </c>
       <c r="U22" t="n">
-        <v>0.039</v>
+        <v>0.5228</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3168</v>
+        <v>-3.9444</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8522</v>
+        <v>-2.0563</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4645</v>
+        <v>-1.8881</v>
       </c>
       <c r="G23" t="n">
         <v>1.7727</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6927</v>
+        <v>-0.3203</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3912</v>
+        <v>0.1871</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0838</v>
+        <v>-0.5074</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0162</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8747</v>
+        <v>-4.8305</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9488</v>
+        <v>-3.1529</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9259</v>
+        <v>-1.6777</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4548</v>
@@ -2326,13 +2326,13 @@
         <v>0.7935</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2959</v>
+        <v>0.3401</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4932</v>
+        <v>0.2891</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1973</v>
+        <v>0.051</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3271</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.43239999999999</v>
+        <v>21.2342</v>
       </c>
       <c r="E25" t="n">
-        <v>15.9215</v>
+        <v>15.9213</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4888</v>
+        <v>5.313000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>15.5957</v>
@@ -2404,13 +2404,13 @@
         <v>15.8706</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.235300000000001</v>
+        <v>0.5666000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9910999999999996</v>
+        <v>-0.9912</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.244100000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="V25" t="n">
         <v>4.080000000000002</v>
